--- a/tests/ExcelRenderer.Formulas.Tests/Fixtures/Oracle/Mapping/mapping-70.xlsx
+++ b/tests/ExcelRenderer.Formulas.Tests/Fixtures/Oracle/Mapping/mapping-70.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice" sheetId="1" r:id="R66113bdc424146c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rates" sheetId="2" r:id="Rf8fd0cfdc96a4e58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="3" r:id="R01d7797ecf1c4544"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice" sheetId="1" r:id="Rfae50922cfa64eae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rates" sheetId="2" r:id="R87193286367c4c38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="3" r:id="R0826921ba1534560"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Amounts">'Invoice'!$D$1:$D$71</x:definedName>
